--- a/informes_data/Tercera FEB/2025-26/Regular_Season/aggregate_individual/AGG_IND_UNIVERSIDAD DE OVIEDO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/aggregate_individual/AGG_IND_UNIVERSIDAD DE OVIEDO.xlsx
@@ -553,7 +553,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>D. DIARRA</t>
+          <t>D. CUETOS FERNANDEZ</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -565,73 +565,73 @@
         <v>26</v>
       </c>
       <c r="D2" t="n">
-        <v>113.6858</v>
+        <v>81.19709999999999</v>
       </c>
       <c r="E2" t="n">
-        <v>80.7495</v>
+        <v>60.4041</v>
       </c>
       <c r="F2" t="n">
-        <v>32.9363</v>
+        <v>20.7928</v>
       </c>
       <c r="G2" t="n">
-        <v>6.9477</v>
+        <v>46.2917</v>
       </c>
       <c r="H2" t="n">
-        <v>20.0607</v>
+        <v>17.7461</v>
       </c>
       <c r="I2" t="n">
-        <v>-13.1128</v>
+        <v>28.5459</v>
       </c>
       <c r="J2" t="n">
-        <v>44.6955</v>
+        <v>76.6537</v>
       </c>
       <c r="K2" t="n">
-        <v>40.9904</v>
+        <v>43.3056</v>
       </c>
       <c r="L2" t="n">
-        <v>3.704800000000001</v>
+        <v>33.3483</v>
       </c>
       <c r="M2" t="n">
-        <v>-37.7474</v>
+        <v>-30.362</v>
       </c>
       <c r="N2" t="n">
-        <v>-20.9294</v>
+        <v>-25.5596</v>
       </c>
       <c r="O2" t="n">
-        <v>-16.8176</v>
+        <v>-4.8021</v>
       </c>
       <c r="P2" t="n">
-        <v>11.9466</v>
+        <v>22.3265</v>
       </c>
       <c r="Q2" t="n">
-        <v>-55.8164</v>
+        <v>-34.0773</v>
       </c>
       <c r="R2" t="n">
-        <v>67.7636</v>
+        <v>56.4041</v>
       </c>
       <c r="S2" t="n">
-        <v>81.553</v>
+        <v>-2.3555</v>
       </c>
       <c r="T2" t="n">
-        <v>62.3449</v>
+        <v>0.9233</v>
       </c>
       <c r="U2" t="n">
-        <v>19.208</v>
+        <v>-3.279</v>
       </c>
       <c r="V2" t="n">
-        <v>13.2383</v>
+        <v>14.9338</v>
       </c>
       <c r="W2" t="n">
-        <v>29.5262</v>
+        <v>16.9051</v>
       </c>
       <c r="X2" t="n">
-        <v>-16.2882</v>
+        <v>-1.9711</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>D. CUETOS FERNANDEZ</t>
+          <t>D. DIARRA</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,67 +643,67 @@
         <v>26</v>
       </c>
       <c r="D3" t="n">
-        <v>67.15989999999999</v>
+        <v>62.6282</v>
       </c>
       <c r="E3" t="n">
-        <v>52.2702</v>
+        <v>39.3532</v>
       </c>
       <c r="F3" t="n">
-        <v>14.8897</v>
+        <v>23.2751</v>
       </c>
       <c r="G3" t="n">
-        <v>46.2917</v>
+        <v>6.9477</v>
       </c>
       <c r="H3" t="n">
-        <v>17.7461</v>
+        <v>20.0607</v>
       </c>
       <c r="I3" t="n">
-        <v>28.5459</v>
+        <v>-13.1128</v>
       </c>
       <c r="J3" t="n">
-        <v>76.6537</v>
+        <v>44.6955</v>
       </c>
       <c r="K3" t="n">
-        <v>43.3056</v>
+        <v>40.9904</v>
       </c>
       <c r="L3" t="n">
-        <v>33.3483</v>
+        <v>3.704800000000001</v>
       </c>
       <c r="M3" t="n">
-        <v>-30.362</v>
+        <v>-37.7474</v>
       </c>
       <c r="N3" t="n">
-        <v>-25.5596</v>
+        <v>-20.9294</v>
       </c>
       <c r="O3" t="n">
-        <v>-4.8021</v>
+        <v>-16.8176</v>
       </c>
       <c r="P3" t="n">
-        <v>22.3265</v>
+        <v>11.9466</v>
       </c>
       <c r="Q3" t="n">
-        <v>-34.0773</v>
+        <v>-55.8164</v>
       </c>
       <c r="R3" t="n">
-        <v>56.4041</v>
+        <v>67.7636</v>
       </c>
       <c r="S3" t="n">
-        <v>-16.3924</v>
+        <v>30.4951</v>
       </c>
       <c r="T3" t="n">
-        <v>-7.210599999999999</v>
+        <v>20.9486</v>
       </c>
       <c r="U3" t="n">
-        <v>-9.182</v>
+        <v>9.5465</v>
       </c>
       <c r="V3" t="n">
-        <v>14.9338</v>
+        <v>13.2383</v>
       </c>
       <c r="W3" t="n">
-        <v>16.9051</v>
+        <v>29.5262</v>
       </c>
       <c r="X3" t="n">
-        <v>-1.9711</v>
+        <v>-16.2882</v>
       </c>
     </row>
     <row r="4">
@@ -721,13 +721,13 @@
         <v>26</v>
       </c>
       <c r="D4" t="n">
-        <v>44.44909999999999</v>
+        <v>52.87929999999999</v>
       </c>
       <c r="E4" t="n">
-        <v>39.4762</v>
+        <v>44.1308</v>
       </c>
       <c r="F4" t="n">
-        <v>4.973100000000001</v>
+        <v>8.7485</v>
       </c>
       <c r="G4" t="n">
         <v>34.3182</v>
@@ -766,13 +766,13 @@
         <v>60.517</v>
       </c>
       <c r="S4" t="n">
-        <v>-10.3211</v>
+        <v>-1.8908</v>
       </c>
       <c r="T4" t="n">
-        <v>-7.8769</v>
+        <v>-3.2224</v>
       </c>
       <c r="U4" t="n">
-        <v>-2.4443</v>
+        <v>1.3317</v>
       </c>
       <c r="V4" t="n">
         <v>9.0928</v>
@@ -787,7 +787,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>N. LOPEZ ALVAREZ-TIRADOR</t>
+          <t>M. ZORROZUA HERRERO</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -796,76 +796,76 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D5" t="n">
-        <v>21.4683</v>
+        <v>24.425</v>
       </c>
       <c r="E5" t="n">
-        <v>11.95</v>
+        <v>7.5543</v>
       </c>
       <c r="F5" t="n">
-        <v>9.5181</v>
+        <v>16.8708</v>
       </c>
       <c r="G5" t="n">
-        <v>-3.282000000000002</v>
+        <v>11.6213</v>
       </c>
       <c r="H5" t="n">
-        <v>-4.1498</v>
+        <v>13.1105</v>
       </c>
       <c r="I5" t="n">
-        <v>0.8680999999999994</v>
+        <v>-1.488900000000001</v>
       </c>
       <c r="J5" t="n">
-        <v>25.5548</v>
+        <v>38.4172</v>
       </c>
       <c r="K5" t="n">
-        <v>10.9636</v>
+        <v>34.3161</v>
       </c>
       <c r="L5" t="n">
-        <v>14.5911</v>
+        <v>4.101000000000001</v>
       </c>
       <c r="M5" t="n">
-        <v>-28.8365</v>
+        <v>-26.7955</v>
       </c>
       <c r="N5" t="n">
-        <v>-15.1134</v>
+        <v>-21.2057</v>
       </c>
       <c r="O5" t="n">
-        <v>-13.7232</v>
+        <v>-5.5899</v>
       </c>
       <c r="P5" t="n">
-        <v>30.7481</v>
+        <v>10.5756</v>
       </c>
       <c r="Q5" t="n">
-        <v>-15.2759</v>
+        <v>-45.6322</v>
       </c>
       <c r="R5" t="n">
-        <v>46.0242</v>
+        <v>56.2083</v>
       </c>
       <c r="S5" t="n">
-        <v>-3.0642</v>
+        <v>-0.1503999999999999</v>
       </c>
       <c r="T5" t="n">
-        <v>-1.9655</v>
+        <v>0.7467000000000001</v>
       </c>
       <c r="U5" t="n">
-        <v>-1.0987</v>
+        <v>-0.8970999999999998</v>
       </c>
       <c r="V5" t="n">
-        <v>-2.9337</v>
+        <v>2.3783</v>
       </c>
       <c r="W5" t="n">
-        <v>3.6375</v>
+        <v>14.0236</v>
       </c>
       <c r="X5" t="n">
-        <v>-6.5713</v>
+        <v>-11.6453</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>J. ARIAS GONZALEZ</t>
+          <t>N. LOPEZ ALVAREZ-TIRADOR</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -874,76 +874,76 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>13</v>
+        <v>24</v>
       </c>
       <c r="D6" t="n">
-        <v>20.8933</v>
+        <v>24.0152</v>
       </c>
       <c r="E6" t="n">
-        <v>12.8228</v>
+        <v>13.1256</v>
       </c>
       <c r="F6" t="n">
-        <v>8.070500000000001</v>
+        <v>10.8898</v>
       </c>
       <c r="G6" t="n">
-        <v>1.7042</v>
+        <v>-3.282000000000002</v>
       </c>
       <c r="H6" t="n">
-        <v>-10.8461</v>
+        <v>-4.1498</v>
       </c>
       <c r="I6" t="n">
-        <v>12.5502</v>
+        <v>0.8680999999999994</v>
       </c>
       <c r="J6" t="n">
-        <v>21.1889</v>
+        <v>25.5548</v>
       </c>
       <c r="K6" t="n">
-        <v>6.1851</v>
+        <v>10.9636</v>
       </c>
       <c r="L6" t="n">
-        <v>15.004</v>
+        <v>14.5911</v>
       </c>
       <c r="M6" t="n">
-        <v>-19.4849</v>
+        <v>-28.8365</v>
       </c>
       <c r="N6" t="n">
-        <v>-17.0312</v>
+        <v>-15.1134</v>
       </c>
       <c r="O6" t="n">
-        <v>-2.4538</v>
+        <v>-13.7232</v>
       </c>
       <c r="P6" t="n">
-        <v>6.8546</v>
+        <v>30.7481</v>
       </c>
       <c r="Q6" t="n">
-        <v>-23.8934</v>
+        <v>-15.2759</v>
       </c>
       <c r="R6" t="n">
-        <v>30.7481</v>
+        <v>46.0242</v>
       </c>
       <c r="S6" t="n">
-        <v>10.2803</v>
+        <v>-0.5179000000000002</v>
       </c>
       <c r="T6" t="n">
-        <v>5.0837</v>
+        <v>-0.7907000000000001</v>
       </c>
       <c r="U6" t="n">
-        <v>5.1966</v>
+        <v>0.2729</v>
       </c>
       <c r="V6" t="n">
-        <v>2.0542</v>
+        <v>-2.9337</v>
       </c>
       <c r="W6" t="n">
-        <v>10.4438</v>
+        <v>3.6375</v>
       </c>
       <c r="X6" t="n">
-        <v>-8.3896</v>
+        <v>-6.5713</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>M. ZORROZUA HERRERO</t>
+          <t>J. ARIAS GONZALEZ</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -952,70 +952,70 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>25</v>
+        <v>13</v>
       </c>
       <c r="D7" t="n">
-        <v>14.2323</v>
+        <v>14.3084</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.4607999999999998</v>
+        <v>9.1884</v>
       </c>
       <c r="F7" t="n">
-        <v>14.693</v>
+        <v>5.120299999999999</v>
       </c>
       <c r="G7" t="n">
-        <v>11.6213</v>
+        <v>1.7042</v>
       </c>
       <c r="H7" t="n">
-        <v>13.1105</v>
+        <v>-10.8461</v>
       </c>
       <c r="I7" t="n">
-        <v>-1.488900000000001</v>
+        <v>12.5502</v>
       </c>
       <c r="J7" t="n">
-        <v>38.4172</v>
+        <v>21.1889</v>
       </c>
       <c r="K7" t="n">
-        <v>34.3161</v>
+        <v>6.1851</v>
       </c>
       <c r="L7" t="n">
-        <v>4.101000000000001</v>
+        <v>15.004</v>
       </c>
       <c r="M7" t="n">
-        <v>-26.7955</v>
+        <v>-19.4849</v>
       </c>
       <c r="N7" t="n">
-        <v>-21.2057</v>
+        <v>-17.0312</v>
       </c>
       <c r="O7" t="n">
-        <v>-5.5899</v>
+        <v>-2.4538</v>
       </c>
       <c r="P7" t="n">
-        <v>10.5756</v>
+        <v>6.8546</v>
       </c>
       <c r="Q7" t="n">
-        <v>-45.6322</v>
+        <v>-23.8934</v>
       </c>
       <c r="R7" t="n">
-        <v>56.2083</v>
+        <v>30.7481</v>
       </c>
       <c r="S7" t="n">
-        <v>-10.3427</v>
+        <v>3.6954</v>
       </c>
       <c r="T7" t="n">
-        <v>-7.2682</v>
+        <v>1.449</v>
       </c>
       <c r="U7" t="n">
-        <v>-3.0749</v>
+        <v>2.2462</v>
       </c>
       <c r="V7" t="n">
-        <v>2.3783</v>
+        <v>2.0542</v>
       </c>
       <c r="W7" t="n">
-        <v>14.0236</v>
+        <v>10.4438</v>
       </c>
       <c r="X7" t="n">
-        <v>-11.6453</v>
+        <v>-8.3896</v>
       </c>
     </row>
     <row r="8">
@@ -1033,13 +1033,13 @@
         <v>23</v>
       </c>
       <c r="D8" t="n">
-        <v>4.710999999999999</v>
+        <v>14.2428</v>
       </c>
       <c r="E8" t="n">
-        <v>10.6219</v>
+        <v>17.2472</v>
       </c>
       <c r="F8" t="n">
-        <v>-5.9108</v>
+        <v>-3.0043</v>
       </c>
       <c r="G8" t="n">
         <v>4.0793</v>
@@ -1078,13 +1078,13 @@
         <v>26.635</v>
       </c>
       <c r="S8" t="n">
-        <v>-9.6571</v>
+        <v>-0.1253999999999998</v>
       </c>
       <c r="T8" t="n">
-        <v>-4.4972</v>
+        <v>2.128</v>
       </c>
       <c r="U8" t="n">
-        <v>-5.1598</v>
+        <v>-2.2531</v>
       </c>
       <c r="V8" t="n">
         <v>-0.09130000000000038</v>
@@ -1099,7 +1099,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A. PEREZ REQUENA</t>
+          <t>M. BARTOLOME COBLE</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1108,76 +1108,76 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>1</v>
+        <v>24</v>
       </c>
       <c r="D9" t="n">
-        <v>0.4312</v>
+        <v>3.262299999999999</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.1159</v>
+        <v>7.0783</v>
       </c>
       <c r="F9" t="n">
-        <v>0.5472</v>
+        <v>-3.8163</v>
       </c>
       <c r="G9" t="n">
-        <v>-0.0137</v>
+        <v>-6.6249</v>
       </c>
       <c r="H9" t="n">
-        <v>-0.3675</v>
+        <v>-6.829999999999999</v>
       </c>
       <c r="I9" t="n">
-        <v>0.3537</v>
+        <v>0.2056000000000007</v>
       </c>
       <c r="J9" t="n">
-        <v>0.1217</v>
+        <v>33.0146</v>
       </c>
       <c r="K9" t="n">
-        <v>0.0408</v>
+        <v>18.8285</v>
       </c>
       <c r="L9" t="n">
-        <v>0.0808</v>
+        <v>14.1862</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.1354</v>
+        <v>-39.6392</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.4083</v>
+        <v>-25.6584</v>
       </c>
       <c r="O9" t="n">
-        <v>0.2729</v>
+        <v>-13.9808</v>
       </c>
       <c r="P9" t="n">
-        <v>0.7834</v>
+        <v>10.7716</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>-38.582</v>
       </c>
       <c r="R9" t="n">
-        <v>0.7834</v>
+        <v>49.3537</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.3384</v>
+        <v>-8.3384</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.2376</v>
+        <v>-6.5191</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.1008</v>
+        <v>-1.8192</v>
       </c>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>7.4534</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>19.1656</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>-11.7121</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>J. PEREZ RUIZ</t>
+          <t>R. FERNANDEZ FERNANDEZ</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1186,76 +1186,76 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>10</v>
+        <v>26</v>
       </c>
       <c r="D10" t="n">
-        <v>0.08080000000000043</v>
+        <v>2.505699999999999</v>
       </c>
       <c r="E10" t="n">
-        <v>-1.759</v>
+        <v>5.958899999999999</v>
       </c>
       <c r="F10" t="n">
-        <v>1.8397</v>
+        <v>-3.453</v>
       </c>
       <c r="G10" t="n">
-        <v>-5.0608</v>
+        <v>-14.1007</v>
       </c>
       <c r="H10" t="n">
-        <v>-1.1592</v>
+        <v>-14.7379</v>
       </c>
       <c r="I10" t="n">
-        <v>-3.9017</v>
+        <v>0.637</v>
       </c>
       <c r="J10" t="n">
-        <v>5.1335</v>
+        <v>21.5792</v>
       </c>
       <c r="K10" t="n">
-        <v>6.8558</v>
+        <v>8.672000000000001</v>
       </c>
       <c r="L10" t="n">
-        <v>-1.7222</v>
+        <v>12.9078</v>
       </c>
       <c r="M10" t="n">
-        <v>-10.1946</v>
+        <v>-35.6804</v>
       </c>
       <c r="N10" t="n">
-        <v>-8.0151</v>
+        <v>-23.4098</v>
       </c>
       <c r="O10" t="n">
-        <v>-2.1795</v>
+        <v>-12.2704</v>
       </c>
       <c r="P10" t="n">
-        <v>4.7002</v>
+        <v>30.5524</v>
       </c>
       <c r="Q10" t="n">
-        <v>-8.813000000000001</v>
+        <v>-22.5222</v>
       </c>
       <c r="R10" t="n">
-        <v>13.5133</v>
+        <v>53.0749</v>
       </c>
       <c r="S10" t="n">
-        <v>2.2727</v>
+        <v>-3.114</v>
       </c>
       <c r="T10" t="n">
-        <v>1.2098</v>
+        <v>-2.9783</v>
       </c>
       <c r="U10" t="n">
-        <v>1.0629</v>
+        <v>-0.1354999999999999</v>
       </c>
       <c r="V10" t="n">
-        <v>-1.8314</v>
+        <v>-10.832</v>
       </c>
       <c r="W10" t="n">
-        <v>0.7109999999999999</v>
+        <v>9.880699999999999</v>
       </c>
       <c r="X10" t="n">
-        <v>-2.5423</v>
+        <v>-20.7124</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>R. FERNANDEZ FERNANDEZ</t>
+          <t>A. PEREZ REQUENA</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1264,76 +1264,76 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>26</v>
+        <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-0.7118999999999993</v>
+        <v>0.4847</v>
       </c>
       <c r="E11" t="n">
-        <v>4.126899999999999</v>
+        <v>-0.1159</v>
       </c>
       <c r="F11" t="n">
-        <v>-4.838799999999999</v>
+        <v>0.6006</v>
       </c>
       <c r="G11" t="n">
-        <v>-14.1007</v>
+        <v>-0.0137</v>
       </c>
       <c r="H11" t="n">
-        <v>-14.7379</v>
+        <v>-0.3675</v>
       </c>
       <c r="I11" t="n">
-        <v>0.637</v>
+        <v>0.3537</v>
       </c>
       <c r="J11" t="n">
-        <v>21.5792</v>
+        <v>0.1217</v>
       </c>
       <c r="K11" t="n">
-        <v>8.672000000000001</v>
+        <v>0.0408</v>
       </c>
       <c r="L11" t="n">
-        <v>12.9078</v>
+        <v>0.0808</v>
       </c>
       <c r="M11" t="n">
-        <v>-35.6804</v>
+        <v>-0.1354</v>
       </c>
       <c r="N11" t="n">
-        <v>-23.4098</v>
+        <v>-0.4083</v>
       </c>
       <c r="O11" t="n">
-        <v>-12.2704</v>
+        <v>0.2729</v>
       </c>
       <c r="P11" t="n">
-        <v>30.5524</v>
+        <v>0.7834</v>
       </c>
       <c r="Q11" t="n">
-        <v>-22.5222</v>
+        <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>53.0749</v>
+        <v>0.7834</v>
       </c>
       <c r="S11" t="n">
-        <v>-6.3317</v>
+        <v>-0.285</v>
       </c>
       <c r="T11" t="n">
-        <v>-4.8104</v>
+        <v>-0.2376</v>
       </c>
       <c r="U11" t="n">
-        <v>-1.5213</v>
+        <v>-0.0473</v>
       </c>
       <c r="V11" t="n">
-        <v>-10.832</v>
+        <v>0</v>
       </c>
       <c r="W11" t="n">
-        <v>9.880699999999999</v>
+        <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>-20.7124</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>L. VIDAL MARTIN</t>
+          <t>J. PEREZ RUIZ</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1342,76 +1342,76 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="D12" t="n">
-        <v>-2.1309</v>
+        <v>-0.9167000000000001</v>
       </c>
       <c r="E12" t="n">
-        <v>-3.1053</v>
+        <v>-2.1682</v>
       </c>
       <c r="F12" t="n">
-        <v>0.9743999999999999</v>
+        <v>1.2519</v>
       </c>
       <c r="G12" t="n">
-        <v>-3.887799999999999</v>
+        <v>-5.0608</v>
       </c>
       <c r="H12" t="n">
-        <v>-3.1396</v>
+        <v>-1.1592</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.7482</v>
+        <v>-3.9017</v>
       </c>
       <c r="J12" t="n">
-        <v>-2.7783</v>
+        <v>5.1335</v>
       </c>
       <c r="K12" t="n">
-        <v>-2.125</v>
+        <v>6.8558</v>
       </c>
       <c r="L12" t="n">
-        <v>-0.6533000000000001</v>
+        <v>-1.7222</v>
       </c>
       <c r="M12" t="n">
-        <v>-1.1094</v>
+        <v>-10.1946</v>
       </c>
       <c r="N12" t="n">
-        <v>-1.0145</v>
+        <v>-8.0151</v>
       </c>
       <c r="O12" t="n">
-        <v>-0.09489999999999998</v>
+        <v>-2.1795</v>
       </c>
       <c r="P12" t="n">
-        <v>3.3293</v>
+        <v>4.7002</v>
       </c>
       <c r="Q12" t="n">
-        <v>-0.9792</v>
+        <v>-8.813000000000001</v>
       </c>
       <c r="R12" t="n">
-        <v>4.3086</v>
+        <v>13.5133</v>
       </c>
       <c r="S12" t="n">
-        <v>0.5278</v>
+        <v>1.2752</v>
       </c>
       <c r="T12" t="n">
-        <v>0.3769999999999999</v>
+        <v>0.8003</v>
       </c>
       <c r="U12" t="n">
-        <v>0.1508</v>
+        <v>0.4750000000000001</v>
       </c>
       <c r="V12" t="n">
-        <v>-2.1003</v>
+        <v>-1.8314</v>
       </c>
       <c r="W12" t="n">
-        <v>0.2754</v>
+        <v>0.7109999999999999</v>
       </c>
       <c r="X12" t="n">
-        <v>-2.3757</v>
+        <v>-2.5423</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>I. DIARRA PERNIA</t>
+          <t>L. VIDAL MARTIN</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1420,76 +1420,76 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D13" t="n">
-        <v>-2.646</v>
+        <v>-1.195</v>
       </c>
       <c r="E13" t="n">
-        <v>-1.6211</v>
+        <v>-2.3889</v>
       </c>
       <c r="F13" t="n">
-        <v>-1.0249</v>
+        <v>1.1939</v>
       </c>
       <c r="G13" t="n">
-        <v>-2.7407</v>
+        <v>-3.887799999999999</v>
       </c>
       <c r="H13" t="n">
-        <v>-0.8864</v>
+        <v>-3.1396</v>
       </c>
       <c r="I13" t="n">
-        <v>-1.8543</v>
+        <v>-0.7482</v>
       </c>
       <c r="J13" t="n">
-        <v>-1.3241</v>
+        <v>-2.7783</v>
       </c>
       <c r="K13" t="n">
-        <v>-0.6822</v>
+        <v>-2.125</v>
       </c>
       <c r="L13" t="n">
-        <v>-0.6418</v>
+        <v>-0.6533000000000001</v>
       </c>
       <c r="M13" t="n">
-        <v>-1.4166</v>
+        <v>-1.1094</v>
       </c>
       <c r="N13" t="n">
-        <v>-0.2042</v>
+        <v>-1.0145</v>
       </c>
       <c r="O13" t="n">
-        <v>-1.2125</v>
+        <v>-0.09489999999999998</v>
       </c>
       <c r="P13" t="n">
-        <v>0.3917</v>
+        <v>3.3293</v>
       </c>
       <c r="Q13" t="n">
-        <v>0</v>
+        <v>-0.9792</v>
       </c>
       <c r="R13" t="n">
-        <v>0.3917</v>
+        <v>4.3086</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.297</v>
+        <v>1.4635</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.297</v>
+        <v>1.0933</v>
       </c>
       <c r="U13" t="n">
-        <v>0</v>
+        <v>0.3703</v>
       </c>
       <c r="V13" t="n">
-        <v>0</v>
+        <v>-2.1003</v>
       </c>
       <c r="W13" t="n">
-        <v>0</v>
+        <v>0.2754</v>
       </c>
       <c r="X13" t="n">
-        <v>0</v>
+        <v>-2.3757</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>M. BARTOLOME COBLE</t>
+          <t>I. DIARRA PERNIA</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1498,70 +1498,70 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>24</v>
+        <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>-4.7506</v>
+        <v>-2.5436</v>
       </c>
       <c r="E14" t="n">
-        <v>2.6616</v>
+        <v>-1.5187</v>
       </c>
       <c r="F14" t="n">
-        <v>-7.412100000000001</v>
+        <v>-1.0249</v>
       </c>
       <c r="G14" t="n">
-        <v>-6.6249</v>
+        <v>-2.7407</v>
       </c>
       <c r="H14" t="n">
-        <v>-6.829999999999999</v>
+        <v>-0.8864</v>
       </c>
       <c r="I14" t="n">
-        <v>0.2056000000000007</v>
+        <v>-1.8543</v>
       </c>
       <c r="J14" t="n">
-        <v>33.0146</v>
+        <v>-1.3241</v>
       </c>
       <c r="K14" t="n">
-        <v>18.8285</v>
+        <v>-0.6822</v>
       </c>
       <c r="L14" t="n">
-        <v>14.1862</v>
+        <v>-0.6418</v>
       </c>
       <c r="M14" t="n">
-        <v>-39.6392</v>
+        <v>-1.4166</v>
       </c>
       <c r="N14" t="n">
-        <v>-25.6584</v>
+        <v>-0.2042</v>
       </c>
       <c r="O14" t="n">
-        <v>-13.9808</v>
+        <v>-1.2125</v>
       </c>
       <c r="P14" t="n">
-        <v>10.7716</v>
+        <v>0.3917</v>
       </c>
       <c r="Q14" t="n">
-        <v>-38.582</v>
+        <v>0</v>
       </c>
       <c r="R14" t="n">
-        <v>49.3537</v>
+        <v>0.3917</v>
       </c>
       <c r="S14" t="n">
-        <v>-16.351</v>
+        <v>-0.1947</v>
       </c>
       <c r="T14" t="n">
-        <v>-10.9356</v>
+        <v>-0.1947</v>
       </c>
       <c r="U14" t="n">
-        <v>-5.414800000000001</v>
+        <v>0</v>
       </c>
       <c r="V14" t="n">
-        <v>7.4534</v>
+        <v>0</v>
       </c>
       <c r="W14" t="n">
-        <v>19.1656</v>
+        <v>0</v>
       </c>
       <c r="X14" t="n">
-        <v>-11.7121</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15">
@@ -1579,13 +1579,13 @@
         <v>26</v>
       </c>
       <c r="D15" t="n">
-        <v>-26.1692</v>
+        <v>-14.5739</v>
       </c>
       <c r="E15" t="n">
-        <v>-28.606</v>
+        <v>-19.5514</v>
       </c>
       <c r="F15" t="n">
-        <v>2.436599999999999</v>
+        <v>4.977399999999999</v>
       </c>
       <c r="G15" t="n">
         <v>-26.5267</v>
@@ -1624,13 +1624,13 @@
         <v>54.8374</v>
       </c>
       <c r="S15" t="n">
-        <v>-12.7553</v>
+        <v>-1.1601</v>
       </c>
       <c r="T15" t="n">
-        <v>-8.716100000000001</v>
+        <v>0.3387000000000001</v>
       </c>
       <c r="U15" t="n">
-        <v>-4.0391</v>
+        <v>-1.4985</v>
       </c>
       <c r="V15" t="n">
         <v>-2.751100000000001</v>
@@ -1657,13 +1657,13 @@
         <v>26</v>
       </c>
       <c r="D16" t="n">
-        <v>-57.2778</v>
+        <v>-51.0643</v>
       </c>
       <c r="E16" t="n">
-        <v>-40.6441</v>
+        <v>-36.6628</v>
       </c>
       <c r="F16" t="n">
-        <v>-16.6339</v>
+        <v>-14.4011</v>
       </c>
       <c r="G16" t="n">
         <v>-55.7462</v>
@@ -1702,13 +1702,13 @@
         <v>45.4365</v>
       </c>
       <c r="S16" t="n">
-        <v>-14.4695</v>
+        <v>-8.2562</v>
       </c>
       <c r="T16" t="n">
-        <v>-10.5895</v>
+        <v>-6.6085</v>
       </c>
       <c r="U16" t="n">
-        <v>-3.8801</v>
+        <v>-1.6477</v>
       </c>
       <c r="V16" t="n">
         <v>-9.388499999999999</v>
@@ -1735,31 +1735,31 @@
         <v>26</v>
       </c>
       <c r="D17" t="n">
-        <v>193.4252999999999</v>
+        <v>209.6552</v>
       </c>
       <c r="E17" t="n">
-        <v>138.3669</v>
+        <v>141.6349</v>
       </c>
       <c r="F17" t="n">
-        <v>55.0581</v>
+        <v>68.0215</v>
       </c>
       <c r="G17" t="n">
         <v>-13.02110000000002</v>
       </c>
       <c r="H17" t="n">
-        <v>-9.962599999999995</v>
+        <v>-9.962599999999998</v>
       </c>
       <c r="I17" t="n">
         <v>-3.058499999999999</v>
       </c>
       <c r="J17" t="n">
-        <v>352.4648000000001</v>
+        <v>352.4648</v>
       </c>
       <c r="K17" t="n">
         <v>234.5459</v>
       </c>
       <c r="L17" t="n">
-        <v>117.9198</v>
+        <v>117.9198000000001</v>
       </c>
       <c r="M17" t="n">
         <v>-365.4863</v>
@@ -1780,13 +1780,13 @@
         <v>565.9998000000001</v>
       </c>
       <c r="S17" t="n">
-        <v>-5.686600000000011</v>
+        <v>10.5408</v>
       </c>
       <c r="T17" t="n">
-        <v>4.610800000000008</v>
+        <v>7.876600000000001</v>
       </c>
       <c r="U17" t="n">
-        <v>-10.2975</v>
+        <v>2.665200000000001</v>
       </c>
       <c r="V17" t="n">
         <v>19.2225</v>
